--- a/钢铁.xlsx
+++ b/钢铁.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D2796"/>
+  <dimension ref="B2:D2797"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="10.46484375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
@@ -31421,6 +31421,17 @@
       </c>
       <c r="D2796" t="n">
         <v>3240</v>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="B2797" s="38" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C2797" t="n">
+        <v>3290</v>
+      </c>
+      <c r="D2797" t="n">
+        <v>3220</v>
       </c>
     </row>
   </sheetData>
@@ -58817,7 +58828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:P579"/>
+  <dimension ref="B2:P580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="10.46484375" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
@@ -66789,6 +66800,14 @@
       </c>
       <c r="D579" t="n">
         <v>228.2</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" s="38" t="n">
+        <v>46108</v>
+      </c>
+      <c r="D580" t="n">
+        <v>231.1</v>
       </c>
     </row>
   </sheetData>
@@ -66805,7 +66824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H1027"/>
+  <dimension ref="B2:H1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="10.53125" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
@@ -76656,6 +76675,12 @@
       </c>
     </row>
     <row r="579">
+      <c r="B579" s="38" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C579" t="n">
+        <v>0.433</v>
+      </c>
       <c r="F579" s="45" t="n">
         <v>45423</v>
       </c>
@@ -81592,6 +81617,14 @@
       </c>
       <c r="H1027" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="F1028" s="38" t="n">
+        <v>46107</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/钢铁.xlsx
+++ b/钢铁.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linxi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06370A2C-B342-4799-BDC3-BEA635F902E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A1E680-B2B3-4178-BD41-81D722BE41D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,9 +63,6 @@
   <si>
     <t>螺纹钢：HRB400E：Φ20：汇总价格：上海</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>中钢协会员企业：钢材：库存（旬）</t>
   </si>
   <si>
     <t>万吨</t>
@@ -320,6 +317,10 @@
     <t>螺纹钢：高炉：利润</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>中钢协会员企业：钢材：库存（旬）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -569,11 +570,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -858,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D2839"/>
+  <dimension ref="B2:D2844"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -32084,6 +32085,61 @@
         <v>3320</v>
       </c>
     </row>
+    <row r="2840" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2840" s="4">
+        <v>46160</v>
+      </c>
+      <c r="C2840" s="5">
+        <v>3460</v>
+      </c>
+      <c r="D2840" s="5">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="2841" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2841" s="4">
+        <v>46161</v>
+      </c>
+      <c r="C2841" s="5">
+        <v>3450</v>
+      </c>
+      <c r="D2841" s="5">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="2842" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2842" s="4">
+        <v>46162</v>
+      </c>
+      <c r="C2842" s="5">
+        <v>3450</v>
+      </c>
+      <c r="D2842" s="5">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="2843" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2843" s="4">
+        <v>46163</v>
+      </c>
+      <c r="C2843" s="5">
+        <v>3420</v>
+      </c>
+      <c r="D2843" s="5">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="2844" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2844" s="4">
+        <v>46164</v>
+      </c>
+      <c r="C2844" s="5">
+        <v>3410</v>
+      </c>
+      <c r="D2844" s="5">
+        <v>3290</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32092,7 +32148,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3CC072-F485-452E-B203-E65436B3141E}">
-  <dimension ref="B2:C2854"/>
+  <dimension ref="B2:C2858"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.265625" style="2" customWidth="1"/>
@@ -32101,26 +32157,26 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B2" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="23" t="s">
         <v>72</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B3" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B4" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.4">
@@ -54912,11 +54968,48 @@
         <v>46157</v>
       </c>
       <c r="C2853" s="21">
-        <v>111.5</v>
+        <v>109.95</v>
       </c>
     </row>
     <row r="2854" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B2854" s="20"/>
+      <c r="B2854" s="20">
+        <v>46160</v>
+      </c>
+      <c r="C2854" s="21">
+        <v>108.45</v>
+      </c>
+    </row>
+    <row r="2855" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2855" s="20">
+        <v>46161</v>
+      </c>
+      <c r="C2855" s="21">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2856" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2856" s="20">
+        <v>46162</v>
+      </c>
+      <c r="C2856" s="21">
+        <v>107.25</v>
+      </c>
+    </row>
+    <row r="2857" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2857" s="20">
+        <v>46163</v>
+      </c>
+      <c r="C2857" s="21">
+        <v>105.8</v>
+      </c>
+    </row>
+    <row r="2858" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2858" s="20">
+        <v>46164</v>
+      </c>
+      <c r="C2858" s="21">
+        <v>105.8</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -54939,54 +55032,54 @@
         <v>0</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
+        <v>86</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="H3" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="I3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="L3" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="M3" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="N3" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
@@ -54994,10 +55087,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="F4" s="16">
         <v>1315.65</v>
@@ -55035,7 +55128,7 @@
         <v>1363.7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="16">
         <v>1416.72</v>
@@ -55073,7 +55166,7 @@
         <v>1476.26</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" s="16">
         <v>1433.84</v>
@@ -55111,7 +55204,7 @@
         <v>1476.72</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" s="16">
         <v>1417.41</v>
@@ -55149,7 +55242,7 @@
         <v>1491.72</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" s="16">
         <v>1544.34</v>
@@ -55187,7 +55280,7 @@
         <v>1646.67</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9" s="16">
         <v>1679.03</v>
@@ -55225,7 +55318,7 @@
         <v>1712.79</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" s="16">
         <v>2013.54</v>
@@ -55263,7 +55356,7 @@
         <v>1736.53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" s="16">
         <v>2348.0500000000002</v>
@@ -55301,7 +55394,7 @@
         <v>1735.1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="16">
         <v>2529.29</v>
@@ -55339,7 +55432,7 @@
         <v>1545.18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="16">
         <v>2647.54</v>
@@ -55377,7 +55470,7 @@
         <v>1646.8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="16">
         <v>2643.37</v>
@@ -55415,7 +55508,7 @@
         <v>1667.6</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" s="16">
         <v>2573.33</v>
@@ -55453,7 +55546,7 @@
         <v>1496.28</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" s="16">
         <v>2490.61</v>
@@ -55491,7 +55584,7 @@
         <v>1587.25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" s="16">
         <v>2308.12</v>
@@ -55529,7 +55622,7 @@
         <v>1656.66</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F18" s="16">
         <v>2179.9499999999998</v>
@@ -55567,7 +55660,7 @@
         <v>1582.94</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="16">
         <v>2053.92</v>
@@ -55605,7 +55698,7 @@
         <v>1630.91</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="16">
         <v>1917.1</v>
@@ -55643,7 +55736,7 @@
         <v>1745.65</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="16">
         <v>1827.46</v>
@@ -55669,7 +55762,7 @@
       <c r="M21" s="16">
         <v>1447.1</v>
       </c>
-      <c r="N21" s="37">
+      <c r="N21" s="36">
         <v>1647.9099999999999</v>
       </c>
     </row>
@@ -55681,7 +55774,7 @@
         <v>1637.33</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" s="16">
         <v>1751.7</v>
@@ -55707,7 +55800,7 @@
       <c r="M22" s="16">
         <v>1476.07</v>
       </c>
-      <c r="N22" s="37">
+      <c r="N22" s="36">
         <v>1646.58</v>
       </c>
     </row>
@@ -55719,7 +55812,7 @@
         <v>1637.89</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F23" s="16">
         <v>1688.9</v>
@@ -55744,6 +55837,9 @@
       </c>
       <c r="M23" s="16">
         <v>1430.66</v>
+      </c>
+      <c r="N23" s="2">
+        <v>1575.29</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
@@ -55754,7 +55850,7 @@
         <v>1663.51</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" s="16">
         <v>1615.33</v>
@@ -55779,6 +55875,9 @@
       </c>
       <c r="M24" s="16">
         <v>1398.54</v>
+      </c>
+      <c r="N24" s="2">
+        <v>1556.91</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
@@ -55789,7 +55888,7 @@
         <v>1511.88</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" s="16">
         <v>1543.65</v>
@@ -55824,7 +55923,7 @@
         <v>1550.95</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" s="16">
         <v>1493.57</v>
@@ -55859,7 +55958,7 @@
         <v>1544.57</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F27" s="16">
         <v>1430.24</v>
@@ -55894,7 +55993,7 @@
         <v>1531.51</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F28" s="16">
         <v>1456.93</v>
@@ -55929,7 +56028,7 @@
         <v>1617.33</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F29" s="16">
         <v>1490.21</v>
@@ -55964,7 +56063,7 @@
         <v>1600.13</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" s="16">
         <v>1473.62</v>
@@ -55999,7 +56098,7 @@
         <v>1479.45</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F31" s="16">
         <v>1449.73</v>
@@ -56034,7 +56133,7 @@
         <v>1507.44</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F32" s="16">
         <v>1451.92</v>
@@ -56069,7 +56168,7 @@
         <v>1633.82</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F33" s="16">
         <v>1416.14</v>
@@ -56104,7 +56203,7 @@
         <v>1480.52</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F34" s="16">
         <v>1415.78</v>
@@ -56139,7 +56238,7 @@
         <v>1502.89</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F35" s="16">
         <v>1420.26</v>
@@ -56174,7 +56273,7 @@
         <v>1519</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F36" s="16">
         <v>1419.06</v>
@@ -56209,7 +56308,7 @@
         <v>1438.43</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F37" s="16">
         <v>1415.9</v>
@@ -56244,7 +56343,7 @@
         <v>1434.04</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F38" s="16">
         <v>1431.79</v>
@@ -56279,7 +56378,7 @@
         <v>1467.25</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F39" s="16">
         <v>1433.16</v>
@@ -56314,7 +56413,7 @@
         <v>1242.4100000000001</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F40" s="16">
         <v>1430.13</v>
@@ -56349,7 +56448,7 @@
         <v>1236.1400000000001</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F41" s="16">
         <v>1409.19</v>
@@ -56384,7 +56483,7 @@
         <v>1250.33</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F42" s="16">
         <v>1451.4</v>
@@ -56419,7 +56518,7 @@
         <v>1201.71</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F43" s="16">
         <v>1585.05</v>
@@ -56454,7 +56553,7 @@
         <v>1384.57</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F44" s="16">
         <v>1536.9</v>
@@ -56489,7 +56588,7 @@
         <v>1462.41</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F45" s="16">
         <v>1468.82</v>
@@ -56524,7 +56623,7 @@
         <v>1379.47</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F46" s="16">
         <v>1396.59</v>
@@ -56559,7 +56658,7 @@
         <v>1370.61</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F47" s="16">
         <v>1349.77</v>
@@ -56594,7 +56693,7 @@
         <v>1375.52</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F48" s="16">
         <v>1311.82</v>
@@ -56629,7 +56728,7 @@
         <v>1205.5899999999999</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F49" s="16">
         <v>1301.3499999999999</v>
@@ -56664,7 +56763,7 @@
         <v>1291.3699999999999</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F50" s="16">
         <v>1304.8800000000001</v>
@@ -56699,7 +56798,7 @@
         <v>1300.23</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F51" s="16">
         <v>1305.1099999999999</v>
@@ -56734,7 +56833,7 @@
         <v>1234.3800000000001</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F52" s="16">
         <v>1236.6099999999999</v>
@@ -56769,7 +56868,7 @@
         <v>1381.55</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F53" s="16">
         <v>1237.83</v>
@@ -56804,7 +56903,7 @@
         <v>1398.15</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F54" s="16">
         <v>1214.7</v>
@@ -56839,7 +56938,7 @@
         <v>1396.35</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F55" s="16">
         <v>1226.1400000000001</v>
@@ -59802,75 +59901,75 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
+      <c r="G2" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="18"/>
       <c r="H3" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="K3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="L3" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="M3" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="N3" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="O3" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="P3" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="P3" s="17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="28">
         <v>945.53</v>
@@ -59911,7 +60010,7 @@
         <v>243</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="28">
         <v>946.3</v>
@@ -59952,7 +60051,7 @@
         <v>248.15</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" s="28">
         <v>961.05</v>
@@ -59993,7 +60092,7 @@
         <v>247.94</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" s="28">
         <v>946.76</v>
@@ -60034,7 +60133,7 @@
         <v>245.41</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" s="28">
         <v>933.72</v>
@@ -60075,7 +60174,7 @@
         <v>239.17</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" s="28">
         <v>915.11</v>
@@ -60116,7 +60215,7 @@
         <v>234.16</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" s="28">
         <v>909.61500000000001</v>
@@ -60157,7 +60256,7 @@
         <v>233.48</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" s="28">
         <v>904.12</v>
@@ -60198,7 +60297,7 @@
         <v>232.64</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" s="28">
         <v>933.28</v>
@@ -60239,7 +60338,7 @@
         <v>229.98</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H13" s="28">
         <v>942.26</v>
@@ -60280,7 +60379,7 @@
         <v>231.86</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H14" s="28">
         <v>947.57</v>
@@ -60321,7 +60420,7 @@
         <v>229.67</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H15" s="28">
         <v>934.48</v>
@@ -60362,7 +60461,7 @@
         <v>225.52</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H16" s="28">
         <v>929.52</v>
@@ -60403,7 +60502,7 @@
         <v>233.53</v>
       </c>
       <c r="G17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H17" s="28">
         <v>950.45</v>
@@ -60444,7 +60543,7 @@
         <v>234.73</v>
       </c>
       <c r="G18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H18" s="28">
         <v>966.14</v>
@@ -60485,7 +60584,7 @@
         <v>234.16</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="28">
         <v>974.05</v>
@@ -60526,7 +60625,7 @@
         <v>234.89</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H20" s="28">
         <v>969.62</v>
@@ -60567,7 +60666,7 @@
         <v>235.49</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" s="28">
         <v>985.05</v>
@@ -60608,7 +60707,7 @@
         <v>235.15</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H22" s="28">
         <v>987.74</v>
@@ -60649,7 +60748,7 @@
         <v>235.67</v>
       </c>
       <c r="G23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H23" s="28">
         <v>994.45</v>
@@ -60674,6 +60773,9 @@
       </c>
       <c r="O23" s="28">
         <v>868.35</v>
+      </c>
+      <c r="P23">
+        <v>840.24</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.4">
@@ -60687,7 +60789,7 @@
         <v>235.36</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H24" s="28">
         <v>994.74</v>
@@ -60712,6 +60814,9 @@
       </c>
       <c r="O24" s="28">
         <v>872.44</v>
+      </c>
+      <c r="P24">
+        <v>862.19999999999993</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.4">
@@ -60725,7 +60830,7 @@
         <v>234.65</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H25" s="28">
         <v>1001.55</v>
@@ -60763,7 +60868,7 @@
         <v>234.5</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H26" s="28">
         <v>996.36</v>
@@ -60801,7 +60906,7 @@
         <v>233.5</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H27" s="28">
         <v>980.74</v>
@@ -60839,7 +60944,7 @@
         <v>232.33</v>
       </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H28" s="28">
         <v>982.76</v>
@@ -60877,7 +60982,7 @@
         <v>228.99</v>
       </c>
       <c r="G29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H29" s="28">
         <v>997.96</v>
@@ -60915,7 +61020,7 @@
         <v>226.4</v>
       </c>
       <c r="G30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H30" s="28">
         <v>1004.46</v>
@@ -60953,7 +61058,7 @@
         <v>224.55</v>
       </c>
       <c r="G31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H31" s="28">
         <v>1006.87</v>
@@ -60991,7 +61096,7 @@
         <v>217.92</v>
       </c>
       <c r="G32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H32" s="28">
         <v>1009.71</v>
@@ -61029,7 +61134,7 @@
         <v>219.98</v>
       </c>
       <c r="G33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H33" s="28">
         <v>997.41</v>
@@ -61067,7 +61172,7 @@
         <v>221.58</v>
       </c>
       <c r="G34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H34" s="28">
         <v>1005.7</v>
@@ -61105,7 +61210,7 @@
         <v>222.91</v>
       </c>
       <c r="G35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H35" s="28">
         <v>979.99</v>
@@ -61143,7 +61248,7 @@
         <v>222.85</v>
       </c>
       <c r="G36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H36" s="28">
         <v>991.2</v>
@@ -61181,7 +61286,7 @@
         <v>223.64</v>
       </c>
       <c r="G37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H37" s="28">
         <v>997.77</v>
@@ -61219,7 +61324,7 @@
         <v>221.89</v>
       </c>
       <c r="G38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H38" s="28">
         <v>1003.01</v>
@@ -61257,7 +61362,7 @@
         <v>223.32</v>
       </c>
       <c r="G39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H39" s="28">
         <v>999.46</v>
@@ -61295,7 +61400,7 @@
         <v>226.14</v>
       </c>
       <c r="G40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H40" s="28">
         <v>999.09</v>
@@ -61333,7 +61438,7 @@
         <v>226.85</v>
       </c>
       <c r="G41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H41" s="28">
         <v>997.51</v>
@@ -61371,7 +61476,7 @@
         <v>227.74</v>
       </c>
       <c r="G42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H42" s="28">
         <v>1014.55</v>
@@ -61409,7 +61514,7 @@
         <v>226.14</v>
       </c>
       <c r="G43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H43" s="28">
         <v>1019.24</v>
@@ -61447,7 +61552,7 @@
         <v>223.98</v>
       </c>
       <c r="G44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H44" s="28">
         <v>1036.26</v>
@@ -61485,7 +61590,7 @@
         <v>221.29</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H45" s="28">
         <v>1028.8900000000001</v>
@@ -61523,7 +61628,7 @@
         <v>221.52</v>
       </c>
       <c r="G46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H46" s="28">
         <v>1013.75</v>
@@ -61561,7 +61666,7 @@
         <v>219.51</v>
       </c>
       <c r="G47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H47" s="28">
         <v>1030.28</v>
@@ -61599,7 +61704,7 @@
         <v>219.62</v>
       </c>
       <c r="G48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H48" s="28">
         <v>1024.3499999999999</v>
@@ -61637,7 +61742,7 @@
         <v>217.32</v>
       </c>
       <c r="G49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H49" s="28">
         <v>1033.8</v>
@@ -61675,7 +61780,7 @@
         <v>214.79</v>
       </c>
       <c r="G50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H50" s="28">
         <v>1017.1</v>
@@ -61713,7 +61818,7 @@
         <v>215.08</v>
       </c>
       <c r="G51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H51" s="28">
         <v>1015.68</v>
@@ -61751,7 +61856,7 @@
         <v>213.93</v>
       </c>
       <c r="G52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H52" s="28">
         <v>996.16</v>
@@ -61789,7 +61894,7 @@
         <v>212.62</v>
       </c>
       <c r="G53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H53" s="28">
         <v>957.53</v>
@@ -61827,7 +61932,7 @@
         <v>214</v>
       </c>
       <c r="G54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H54" s="28">
         <v>961.76</v>
@@ -61865,7 +61970,7 @@
         <v>218</v>
       </c>
       <c r="G55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H55" s="28">
         <v>970.32</v>
@@ -67753,7 +67858,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A30EC3-E6ED-4809-B571-A03C32366791}">
-  <dimension ref="B2:H1071"/>
+  <dimension ref="B2:H1077"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -67769,16 +67874,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
@@ -67786,7 +67891,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" s="29" t="s">
         <v>1</v>
@@ -67800,10 +67905,10 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" s="29" t="s">
         <v>3</v>
@@ -83032,6 +83137,64 @@
       <c r="H1071" s="5">
         <v>188</v>
       </c>
+    </row>
+    <row r="1072" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1072" s="34">
+        <v>46160</v>
+      </c>
+      <c r="G1072" s="5">
+        <v>134</v>
+      </c>
+      <c r="H1072" s="5">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="1073" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1073" s="34">
+        <v>46161</v>
+      </c>
+      <c r="G1073" s="5">
+        <v>123</v>
+      </c>
+      <c r="H1073" s="5">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="1074" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1074" s="34">
+        <v>46162</v>
+      </c>
+      <c r="G1074" s="5">
+        <v>115</v>
+      </c>
+      <c r="H1074" s="5">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1075" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1075" s="34">
+        <v>46163</v>
+      </c>
+      <c r="G1075" s="5">
+        <v>111</v>
+      </c>
+      <c r="H1075" s="5">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1076" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1076" s="34">
+        <v>46164</v>
+      </c>
+      <c r="G1076" s="5">
+        <v>111</v>
+      </c>
+      <c r="H1076" s="5">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1077" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1077" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/钢铁.xlsx
+++ b/钢铁.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linxi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A1E680-B2B3-4178-BD41-81D722BE41D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23295A55-2A69-4660-B1C4-65ECDED8CB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="钢价" sheetId="1" r:id="rId1"/>
@@ -330,7 +330,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,8 +426,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,8 +445,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -458,6 +469,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -469,7 +495,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -575,6 +601,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -859,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D2844"/>
+  <dimension ref="B2:D2849"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -32137,7 +32166,62 @@
         <v>3410</v>
       </c>
       <c r="D2844" s="5">
-        <v>3290</v>
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="2845" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2845" s="4">
+        <v>46167</v>
+      </c>
+      <c r="C2845" s="5">
+        <v>3460</v>
+      </c>
+      <c r="D2845" s="5">
+        <v>3310</v>
+      </c>
+    </row>
+    <row r="2846" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2846" s="4">
+        <v>46168</v>
+      </c>
+      <c r="C2846" s="5">
+        <v>3410</v>
+      </c>
+      <c r="D2846" s="5">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="2847" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2847" s="4">
+        <v>46169</v>
+      </c>
+      <c r="C2847" s="5">
+        <v>3400</v>
+      </c>
+      <c r="D2847" s="5">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="2848" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2848" s="4">
+        <v>46170</v>
+      </c>
+      <c r="C2848" s="5">
+        <v>3400</v>
+      </c>
+      <c r="D2848" s="5">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="2849" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2849" s="4">
+        <v>46171</v>
+      </c>
+      <c r="C2849" s="5">
+        <v>3410</v>
+      </c>
+      <c r="D2849" s="5">
+        <v>3270</v>
       </c>
     </row>
   </sheetData>
@@ -32148,7 +32232,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3CC072-F485-452E-B203-E65436B3141E}">
-  <dimension ref="B2:C2858"/>
+  <dimension ref="B2:C2863"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.265625" style="2" customWidth="1"/>
@@ -55008,7 +55092,47 @@
         <v>46164</v>
       </c>
       <c r="C2858" s="21">
-        <v>105.8</v>
+        <v>106.25</v>
+      </c>
+    </row>
+    <row r="2859" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2859" s="20">
+        <v>46167</v>
+      </c>
+      <c r="C2859" s="21">
+        <v>106.8</v>
+      </c>
+    </row>
+    <row r="2860" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2860" s="20">
+        <v>46168</v>
+      </c>
+      <c r="C2860" s="21">
+        <v>105.1</v>
+      </c>
+    </row>
+    <row r="2861" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2861" s="20">
+        <v>46169</v>
+      </c>
+      <c r="C2861" s="21">
+        <v>105.1</v>
+      </c>
+    </row>
+    <row r="2862" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2862" s="20">
+        <v>46170</v>
+      </c>
+      <c r="C2862" s="21">
+        <v>105.35</v>
+      </c>
+    </row>
+    <row r="2863" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2863" s="20">
+        <v>46171</v>
+      </c>
+      <c r="C2863" s="21">
+        <v>105.35</v>
       </c>
     </row>
   </sheetData>
@@ -55914,6 +56038,9 @@
       <c r="M25" s="16">
         <v>1365.6</v>
       </c>
+      <c r="N25" s="36">
+        <v>1544.44</v>
+      </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" s="8">
@@ -59830,8 +59957,12 @@
       </c>
     </row>
     <row r="414" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B414" s="12"/>
-      <c r="C414" s="13"/>
+      <c r="B414" s="12">
+        <v>46162</v>
+      </c>
+      <c r="C414" s="13">
+        <v>1877.48</v>
+      </c>
     </row>
     <row r="415" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B415" s="12"/>
@@ -60856,6 +60987,9 @@
       <c r="O25" s="28">
         <v>880.85000000000014</v>
       </c>
+      <c r="P25" s="38">
+        <v>863.72</v>
+      </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B26" s="4">
@@ -67839,13 +67973,37 @@
       </c>
     </row>
     <row r="587" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B587" s="4"/>
+      <c r="B587" s="4">
+        <v>46157</v>
+      </c>
+      <c r="C587" s="5">
+        <v>83.52</v>
+      </c>
+      <c r="D587" s="5">
+        <v>239.33</v>
+      </c>
     </row>
     <row r="588" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B588" s="4"/>
+      <c r="B588" s="4">
+        <v>46164</v>
+      </c>
+      <c r="C588" s="5">
+        <v>84.14</v>
+      </c>
+      <c r="D588" s="5">
+        <v>240.81</v>
+      </c>
     </row>
     <row r="589" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B589" s="4"/>
+      <c r="B589" s="4">
+        <v>46171</v>
+      </c>
+      <c r="C589" s="5">
+        <v>84.14</v>
+      </c>
+      <c r="D589" s="5">
+        <v>241</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -67858,7 +68016,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A30EC3-E6ED-4809-B571-A03C32366791}">
-  <dimension ref="B2:H1077"/>
+  <dimension ref="B2:H1081"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -83190,11 +83348,63 @@
         <v>111</v>
       </c>
       <c r="H1076" s="5">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1077" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F1077" s="34"/>
+      <c r="F1077" s="34">
+        <v>46167</v>
+      </c>
+      <c r="G1077" s="5">
+        <v>136</v>
+      </c>
+      <c r="H1077" s="5">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1078" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1078" s="34">
+        <v>46168</v>
+      </c>
+      <c r="G1078" s="5">
+        <v>120</v>
+      </c>
+      <c r="H1078" s="5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1079" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1079" s="34">
+        <v>46169</v>
+      </c>
+      <c r="G1079" s="5">
+        <v>100</v>
+      </c>
+      <c r="H1079" s="5">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1080" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1080" s="34">
+        <v>46170</v>
+      </c>
+      <c r="G1080" s="5">
+        <v>98</v>
+      </c>
+      <c r="H1080" s="5">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1081" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1081" s="34">
+        <v>46171</v>
+      </c>
+      <c r="G1081" s="5">
+        <v>98</v>
+      </c>
+      <c r="H1081" s="5">
+        <v>155</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/钢铁.xlsx
+++ b/钢铁.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenpe\Desktop\实习202606\平安V2\delink版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6E6ACFC-5E8C-4455-8FE2-73C5FAE6CFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89BCD09C-B56B-4433-980E-17DB2B148A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8828" yWindow="1245" windowWidth="16200" windowHeight="10455" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="钢价" sheetId="1" r:id="rId1"/>
@@ -894,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D2864"/>
+  <dimension ref="B2:D2871"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -32374,10 +32374,71 @@
       </c>
     </row>
     <row r="2863" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2863" s="4"/>
+      <c r="B2863" s="4">
+        <v>46185</v>
+      </c>
+      <c r="C2863" s="5">
+        <v>3380</v>
+      </c>
+      <c r="D2863" s="5">
+        <v>3250</v>
+      </c>
     </row>
     <row r="2864" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2864" s="4"/>
+      <c r="B2864" s="4">
+        <v>46186</v>
+      </c>
+      <c r="C2864" s="5">
+        <v>3380</v>
+      </c>
+      <c r="D2864" s="5">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="2865" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2865" s="4">
+        <v>46187</v>
+      </c>
+      <c r="C2865" s="5">
+        <v>3380</v>
+      </c>
+      <c r="D2865" s="5">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="2866" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2866" s="4">
+        <v>46188</v>
+      </c>
+      <c r="C2866" s="5">
+        <v>3400</v>
+      </c>
+      <c r="D2866" s="5">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="2867" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2867" s="4">
+        <v>46189</v>
+      </c>
+      <c r="C2867" s="5">
+        <v>3390</v>
+      </c>
+      <c r="D2867" s="5">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="2868" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2868" s="4"/>
+    </row>
+    <row r="2869" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2869" s="4"/>
+    </row>
+    <row r="2870" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2870" s="4"/>
+    </row>
+    <row r="2871" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2871" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -32387,7 +32448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3CC072-F485-452E-B203-E65436B3141E}">
-  <dimension ref="B2:C2880"/>
+  <dimension ref="B2:C2885"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.265625" style="2" customWidth="1"/>
@@ -55387,20 +55448,68 @@
       </c>
     </row>
     <row r="2876" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B2876" s="20"/>
-      <c r="C2876" s="21"/>
+      <c r="B2876" s="20">
+        <v>46184</v>
+      </c>
+      <c r="C2876" s="21">
+        <v>101.35</v>
+      </c>
     </row>
     <row r="2877" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C2877" s="21"/>
+      <c r="B2877" s="20">
+        <v>46185</v>
+      </c>
+      <c r="C2877" s="21">
+        <v>101.5</v>
+      </c>
     </row>
     <row r="2878" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C2878" s="21"/>
+      <c r="B2878" s="20">
+        <v>46186</v>
+      </c>
+      <c r="C2878" s="21">
+        <v>101.5</v>
+      </c>
     </row>
     <row r="2879" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C2879" s="21"/>
+      <c r="B2879" s="20">
+        <v>46187</v>
+      </c>
+      <c r="C2879" s="21">
+        <v>101.5</v>
+      </c>
     </row>
     <row r="2880" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C2880" s="21"/>
+      <c r="B2880" s="20">
+        <v>46188</v>
+      </c>
+      <c r="C2880" s="21">
+        <v>102.2</v>
+      </c>
+    </row>
+    <row r="2881" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2881" s="20">
+        <v>46189</v>
+      </c>
+      <c r="C2881" s="21">
+        <v>101.35</v>
+      </c>
+    </row>
+    <row r="2882" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2882" s="20"/>
+      <c r="C2882" s="21"/>
+    </row>
+    <row r="2883" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2883" s="20"/>
+      <c r="C2883" s="21"/>
+    </row>
+    <row r="2884" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2884" s="20"/>
+      <c r="C2884" s="21"/>
+    </row>
+    <row r="2885" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2885" s="20"/>
+      <c r="C2885" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -60311,7 +60420,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4E7A9-1159-49D6-8A41-2BD0E2B7AE9B}">
-  <dimension ref="B2:P596"/>
+  <dimension ref="B2:P597"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -68343,6 +68452,9 @@
     </row>
     <row r="596" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B596" s="4"/>
+    </row>
+    <row r="597" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B597" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -68355,7 +68467,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A30EC3-E6ED-4809-B571-A03C32366791}">
-  <dimension ref="B2:H1097"/>
+  <dimension ref="B2:H1101"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -83889,13 +84001,65 @@
       </c>
     </row>
     <row r="1095" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F1095" s="34"/>
+      <c r="F1095" s="34">
+        <v>46185</v>
+      </c>
+      <c r="G1095" s="5">
+        <v>55</v>
+      </c>
+      <c r="H1095" s="5">
+        <v>113</v>
+      </c>
     </row>
     <row r="1096" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F1096" s="34"/>
+      <c r="F1096" s="34">
+        <v>46186</v>
+      </c>
+      <c r="G1096" s="5">
+        <v>55</v>
+      </c>
+      <c r="H1096" s="5">
+        <v>113</v>
+      </c>
     </row>
     <row r="1097" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F1097" s="34"/>
+      <c r="F1097" s="34">
+        <v>46187</v>
+      </c>
+      <c r="G1097" s="5">
+        <v>55</v>
+      </c>
+      <c r="H1097" s="5">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1098" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1098" s="34">
+        <v>46188</v>
+      </c>
+      <c r="G1098" s="5">
+        <v>51</v>
+      </c>
+      <c r="H1098" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1099" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1099" s="34">
+        <v>46189</v>
+      </c>
+      <c r="G1099" s="5">
+        <v>31</v>
+      </c>
+      <c r="H1099" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1100" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1100" s="34"/>
+    </row>
+    <row r="1101" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1101" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/钢铁.xlsx
+++ b/钢铁.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenpe\Desktop\实习202606\平安V2\delink版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89BCD09C-B56B-4433-980E-17DB2B148A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEF8EDCB-9918-4CE8-81B4-778104ABB15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8828" yWindow="1245" windowWidth="16200" windowHeight="10455" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="钢价" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="88">
   <si>
     <t>指标名称</t>
   </si>
@@ -894,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D2871"/>
+  <dimension ref="B2:D2876"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -32429,16 +32429,103 @@
       </c>
     </row>
     <row r="2868" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2868" s="4"/>
+      <c r="B2868" s="4">
+        <v>46190</v>
+      </c>
+      <c r="C2868" s="5">
+        <v>3380</v>
+      </c>
+      <c r="D2868" s="5">
+        <v>3250</v>
+      </c>
     </row>
     <row r="2869" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2869" s="4"/>
+      <c r="B2869" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C2869" s="5">
+        <v>3360</v>
+      </c>
+      <c r="D2869" s="5">
+        <v>3230</v>
+      </c>
     </row>
     <row r="2870" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2870" s="4"/>
+      <c r="B2870" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C2870" s="5">
+        <v>3360</v>
+      </c>
+      <c r="D2870" s="5">
+        <v>3230</v>
+      </c>
     </row>
     <row r="2871" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2871" s="4"/>
+      <c r="B2871" s="4">
+        <v>46193</v>
+      </c>
+      <c r="C2871" s="5">
+        <v>3360</v>
+      </c>
+      <c r="D2871" s="5">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="2872" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2872" s="4">
+        <v>46194</v>
+      </c>
+      <c r="C2872" s="5">
+        <v>3360</v>
+      </c>
+      <c r="D2872" s="5">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="2873" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2873" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C2873" s="5">
+        <v>3360</v>
+      </c>
+      <c r="D2873" s="5">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="2874" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2874" s="4">
+        <v>46196</v>
+      </c>
+      <c r="C2874" s="5">
+        <v>3350</v>
+      </c>
+      <c r="D2874" s="5">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="2875" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2875" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C2875" s="5">
+        <v>3350</v>
+      </c>
+      <c r="D2875" s="5">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="2876" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2876" s="4">
+        <v>46198</v>
+      </c>
+      <c r="C2876" s="5">
+        <v>3340</v>
+      </c>
+      <c r="D2876" s="5">
+        <v>3210</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -32448,7 +32535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3CC072-F485-452E-B203-E65436B3141E}">
-  <dimension ref="B2:C2885"/>
+  <dimension ref="B2:C2890"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.265625" style="2" customWidth="1"/>
@@ -55496,20 +55583,76 @@
       </c>
     </row>
     <row r="2882" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B2882" s="20"/>
-      <c r="C2882" s="21"/>
+      <c r="B2882" s="20">
+        <v>46190</v>
+      </c>
+      <c r="C2882" s="21">
+        <v>99.25</v>
+      </c>
     </row>
     <row r="2883" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B2883" s="20"/>
-      <c r="C2883" s="21"/>
+      <c r="B2883" s="20">
+        <v>46191</v>
+      </c>
+      <c r="C2883" s="21">
+        <v>99.7</v>
+      </c>
     </row>
     <row r="2884" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B2884" s="20"/>
-      <c r="C2884" s="21"/>
+      <c r="B2884" s="20">
+        <v>46192</v>
+      </c>
+      <c r="C2884" s="21">
+        <v>98.85</v>
+      </c>
     </row>
     <row r="2885" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B2885" s="20"/>
-      <c r="C2885" s="21"/>
+      <c r="B2885" s="20">
+        <v>46193</v>
+      </c>
+      <c r="C2885" s="21">
+        <v>98.85</v>
+      </c>
+    </row>
+    <row r="2886" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2886" s="20">
+        <v>46194</v>
+      </c>
+      <c r="C2886" s="21">
+        <v>98.85</v>
+      </c>
+    </row>
+    <row r="2887" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2887" s="20">
+        <v>46195</v>
+      </c>
+      <c r="C2887" s="21">
+        <v>97.6</v>
+      </c>
+    </row>
+    <row r="2888" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2888" s="20">
+        <v>46196</v>
+      </c>
+      <c r="C2888" s="21">
+        <v>96.85</v>
+      </c>
+    </row>
+    <row r="2889" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2889" s="20">
+        <v>46197</v>
+      </c>
+      <c r="C2889" s="21">
+        <v>98.45</v>
+      </c>
+    </row>
+    <row r="2890" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2890" s="20">
+        <v>46198</v>
+      </c>
+      <c r="C2890" s="21">
+        <v>97.55</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -56528,8 +56671,8 @@
       <c r="M28" s="16">
         <v>1338.89</v>
       </c>
-      <c r="N28" s="36" t="s">
-        <v>87</v>
+      <c r="N28" s="36">
+        <v>1557.02</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
@@ -56566,8 +56709,8 @@
       <c r="M29" s="16">
         <v>1340.03</v>
       </c>
-      <c r="N29" s="36" t="s">
-        <v>87</v>
+      <c r="N29" s="36">
+        <v>1600.9899999999998</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.4">
@@ -60370,12 +60513,20 @@
       </c>
     </row>
     <row r="416" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B416" s="12"/>
-      <c r="C416" s="13"/>
+      <c r="B416" s="12">
+        <v>46183</v>
+      </c>
+      <c r="C416" s="13">
+        <v>1686.61</v>
+      </c>
     </row>
     <row r="417" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B417" s="12"/>
-      <c r="C417" s="13"/>
+      <c r="B417" s="12">
+        <v>46193</v>
+      </c>
+      <c r="C417" s="13">
+        <v>1790</v>
+      </c>
     </row>
     <row r="418" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B418" s="12"/>
@@ -61511,8 +61662,8 @@
       <c r="O28" s="28">
         <v>868.5100000000001</v>
       </c>
-      <c r="P28" s="37" t="s">
-        <v>87</v>
+      <c r="P28" s="37">
+        <v>868.02</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.4">
@@ -61552,6 +61703,9 @@
       <c r="O29" s="28">
         <v>881.09</v>
       </c>
+      <c r="P29" s="37">
+        <v>858.91</v>
+      </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B30" s="4">
@@ -61590,6 +61744,9 @@
       <c r="O30" s="28">
         <v>885.16000000000008</v>
       </c>
+      <c r="P30" s="37" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B31" s="4">
@@ -68439,21 +68596,37 @@
       <c r="E591" s="38"/>
     </row>
     <row r="592" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B592" s="4"/>
-    </row>
-    <row r="593" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B593" s="4"/>
-    </row>
-    <row r="594" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B592" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C592" s="5">
+        <v>84.25</v>
+      </c>
+      <c r="D592" s="5">
+        <v>242.24</v>
+      </c>
+    </row>
+    <row r="593" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B593" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C593" s="5">
+        <v>84.41</v>
+      </c>
+      <c r="D593" s="5">
+        <v>242.95</v>
+      </c>
+    </row>
+    <row r="594" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B594" s="4"/>
     </row>
-    <row r="595" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="595" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B595" s="4"/>
     </row>
-    <row r="596" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="596" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B596" s="4"/>
     </row>
-    <row r="597" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="597" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B597" s="4"/>
     </row>
   </sheetData>
@@ -68467,7 +68640,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A30EC3-E6ED-4809-B571-A03C32366791}">
-  <dimension ref="B2:H1101"/>
+  <dimension ref="B2:H1108"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -78390,7 +78563,12 @@
       </c>
     </row>
     <row r="585" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B585" s="4"/>
+      <c r="B585" s="4">
+        <v>46143</v>
+      </c>
+      <c r="C585" s="5">
+        <v>51.08</v>
+      </c>
       <c r="F585" s="30">
         <v>45432</v>
       </c>
@@ -78402,6 +78580,12 @@
       </c>
     </row>
     <row r="586" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B586" s="4">
+        <v>46150</v>
+      </c>
+      <c r="C586" s="5">
+        <v>60.17</v>
+      </c>
       <c r="F586" s="30">
         <v>45433</v>
       </c>
@@ -78413,6 +78597,12 @@
       </c>
     </row>
     <row r="587" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B587" s="4">
+        <v>46157</v>
+      </c>
+      <c r="C587" s="5">
+        <v>64.069999999999993</v>
+      </c>
       <c r="F587" s="30">
         <v>45434</v>
       </c>
@@ -78424,6 +78614,12 @@
       </c>
     </row>
     <row r="588" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B588" s="4">
+        <v>46164</v>
+      </c>
+      <c r="C588" s="5">
+        <v>63.2</v>
+      </c>
       <c r="F588" s="30">
         <v>45435</v>
       </c>
@@ -78435,6 +78631,12 @@
       </c>
     </row>
     <row r="589" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B589" s="4">
+        <v>46171</v>
+      </c>
+      <c r="C589" s="5">
+        <v>62.34</v>
+      </c>
       <c r="F589" s="30">
         <v>45436</v>
       </c>
@@ -78446,6 +78648,12 @@
       </c>
     </row>
     <row r="590" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B590" s="4">
+        <v>46178</v>
+      </c>
+      <c r="C590" s="5">
+        <v>59.31</v>
+      </c>
       <c r="F590" s="30">
         <v>45439</v>
       </c>
@@ -78457,6 +78665,12 @@
       </c>
     </row>
     <row r="591" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B591" s="4">
+        <v>46185</v>
+      </c>
+      <c r="C591" s="5">
+        <v>55.84</v>
+      </c>
       <c r="F591" s="30">
         <v>45440</v>
       </c>
@@ -78468,6 +78682,12 @@
       </c>
     </row>
     <row r="592" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B592" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C592" s="5">
+        <v>55.84</v>
+      </c>
       <c r="F592" s="30">
         <v>45441</v>
       </c>
@@ -78478,7 +78698,13 @@
         <v>86</v>
       </c>
     </row>
-    <row r="593" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="593" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B593" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C593" s="5">
+        <v>51.08</v>
+      </c>
       <c r="F593" s="30">
         <v>45442</v>
       </c>
@@ -78489,7 +78715,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="594" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="594" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F594" s="30">
         <v>45443</v>
       </c>
@@ -78500,7 +78726,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="595" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="595" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F595" s="30">
         <v>45446</v>
       </c>
@@ -78511,7 +78737,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="596" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="596" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F596" s="30">
         <v>45447</v>
       </c>
@@ -78522,7 +78748,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="597" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="597" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F597" s="30">
         <v>45448</v>
       </c>
@@ -78533,7 +78759,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="598" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="598" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F598" s="30">
         <v>45449</v>
       </c>
@@ -78544,7 +78770,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="599" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="599" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F599" s="30">
         <v>45450</v>
       </c>
@@ -78555,7 +78781,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="600" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="600" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F600" s="30">
         <v>45454</v>
       </c>
@@ -78566,7 +78792,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="601" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="601" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F601" s="30">
         <v>45455</v>
       </c>
@@ -78577,7 +78803,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="602" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="602" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F602" s="30">
         <v>45456</v>
       </c>
@@ -78588,7 +78814,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="603" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="603" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F603" s="30">
         <v>45457</v>
       </c>
@@ -78599,7 +78825,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="604" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="604" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F604" s="30">
         <v>45460</v>
       </c>
@@ -78610,7 +78836,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="605" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="605" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F605" s="30">
         <v>45461</v>
       </c>
@@ -78621,7 +78847,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="606" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="606" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F606" s="30">
         <v>45462</v>
       </c>
@@ -78632,7 +78858,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="607" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="607" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F607" s="30">
         <v>45463</v>
       </c>
@@ -78643,7 +78869,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="608" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="608" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F608" s="30">
         <v>45464</v>
       </c>
@@ -84056,10 +84282,103 @@
       </c>
     </row>
     <row r="1100" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F1100" s="34"/>
+      <c r="F1100" s="34">
+        <v>46190</v>
+      </c>
+      <c r="G1100" s="5">
+        <v>35</v>
+      </c>
+      <c r="H1100" s="5">
+        <v>97</v>
+      </c>
     </row>
     <row r="1101" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F1101" s="34"/>
+      <c r="F1101" s="34">
+        <v>46191</v>
+      </c>
+      <c r="G1101" s="5">
+        <v>37</v>
+      </c>
+      <c r="H1101" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1102" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1102" s="34">
+        <v>46192</v>
+      </c>
+      <c r="G1102" s="5">
+        <v>37</v>
+      </c>
+      <c r="H1102" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1103" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1103" s="34">
+        <v>46193</v>
+      </c>
+      <c r="G1103" s="5">
+        <v>37</v>
+      </c>
+      <c r="H1103" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1104" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1104" s="34">
+        <v>46194</v>
+      </c>
+      <c r="G1104" s="5">
+        <v>37</v>
+      </c>
+      <c r="H1104" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1105" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1105" s="34">
+        <v>46195</v>
+      </c>
+      <c r="G1105" s="5">
+        <v>23</v>
+      </c>
+      <c r="H1105" s="5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="1106" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1106" s="34">
+        <v>46196</v>
+      </c>
+      <c r="G1106" s="5">
+        <v>5</v>
+      </c>
+      <c r="H1106" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1107" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1107" s="34">
+        <v>46197</v>
+      </c>
+      <c r="G1107" s="5">
+        <v>-5</v>
+      </c>
+      <c r="H1107" s="5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1108" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1108" s="34">
+        <v>46198</v>
+      </c>
+      <c r="G1108" s="5">
+        <v>-2</v>
+      </c>
+      <c r="H1108" s="5">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/钢铁.xlsx
+++ b/钢铁.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenpe\Desktop\实习202606\平安V2\delink版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEF8EDCB-9918-4CE8-81B4-778104ABB15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F79151-4D24-464C-8298-B7B62A22D206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="88">
   <si>
     <t>指标名称</t>
   </si>
@@ -894,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D2876"/>
+  <dimension ref="B2:D2884"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -32527,6 +32527,86 @@
         <v>3210</v>
       </c>
     </row>
+    <row r="2877" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2877" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C2877" s="5">
+        <v>3340</v>
+      </c>
+      <c r="D2877" s="5">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="2878" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2878" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C2878" s="5">
+        <v>3340</v>
+      </c>
+      <c r="D2878" s="5">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="2879" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2879" s="4">
+        <v>46201</v>
+      </c>
+      <c r="C2879" s="5">
+        <v>3340</v>
+      </c>
+      <c r="D2879" s="5">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="2880" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2880" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C2880" s="5">
+        <v>3340</v>
+      </c>
+      <c r="D2880" s="5">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="2881" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2881" s="4">
+        <v>46203</v>
+      </c>
+      <c r="C2881" s="5">
+        <v>3340</v>
+      </c>
+      <c r="D2881" s="5">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="2882" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2882" s="4">
+        <v>46204</v>
+      </c>
+      <c r="C2882" s="5">
+        <v>3320</v>
+      </c>
+      <c r="D2882" s="5">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="2883" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2883" s="4">
+        <v>46205</v>
+      </c>
+      <c r="C2883" s="5">
+        <v>3310</v>
+      </c>
+      <c r="D2883" s="5">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="2884" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2884" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32535,7 +32615,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3CC072-F485-452E-B203-E65436B3141E}">
-  <dimension ref="B2:C2890"/>
+  <dimension ref="B2:C2897"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.265625" style="2" customWidth="1"/>
@@ -55652,6 +55732,62 @@
       </c>
       <c r="C2890" s="21">
         <v>97.55</v>
+      </c>
+    </row>
+    <row r="2891" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2891" s="20">
+        <v>46199</v>
+      </c>
+      <c r="C2891" s="21">
+        <v>98.7</v>
+      </c>
+    </row>
+    <row r="2892" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2892" s="20">
+        <v>46200</v>
+      </c>
+      <c r="C2892" s="21">
+        <v>98.7</v>
+      </c>
+    </row>
+    <row r="2893" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2893" s="20">
+        <v>46201</v>
+      </c>
+      <c r="C2893" s="21">
+        <v>98.7</v>
+      </c>
+    </row>
+    <row r="2894" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2894" s="20">
+        <v>46202</v>
+      </c>
+      <c r="C2894" s="21">
+        <v>98.9</v>
+      </c>
+    </row>
+    <row r="2895" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2895" s="20">
+        <v>46203</v>
+      </c>
+      <c r="C2895" s="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2896" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2896" s="20">
+        <v>46204</v>
+      </c>
+      <c r="C2896" s="21">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="2897" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2897" s="20">
+        <v>46205</v>
+      </c>
+      <c r="C2897" s="21">
+        <v>97.5</v>
       </c>
     </row>
   </sheetData>
@@ -56747,8 +56883,8 @@
       <c r="M30" s="16">
         <v>1339.93</v>
       </c>
-      <c r="N30" s="36" t="s">
-        <v>87</v>
+      <c r="N30" s="36">
+        <v>1623.0500000000002</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.4">
@@ -61744,8 +61880,8 @@
       <c r="O30" s="28">
         <v>885.16000000000008</v>
       </c>
-      <c r="P30" s="37" t="s">
-        <v>87</v>
+      <c r="P30" s="37">
+        <v>864.16000000000008</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.4">
@@ -61785,6 +61921,9 @@
       <c r="O31" s="28">
         <v>872.72</v>
       </c>
+      <c r="P31" s="37" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B32" s="4">
@@ -68618,7 +68757,15 @@
       </c>
     </row>
     <row r="594" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B594" s="4"/>
+      <c r="B594" s="4">
+        <v>46206</v>
+      </c>
+      <c r="C594" s="5">
+        <v>83.99</v>
+      </c>
+      <c r="D594" s="5">
+        <v>243.25</v>
+      </c>
     </row>
     <row r="595" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B595" s="4"/>
@@ -68640,7 +68787,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A30EC3-E6ED-4809-B571-A03C32366791}">
-  <dimension ref="B2:H1108"/>
+  <dimension ref="B2:H1116"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -78716,6 +78863,12 @@
       </c>
     </row>
     <row r="594" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B594" s="4">
+        <v>46206</v>
+      </c>
+      <c r="C594" s="5">
+        <v>42.86</v>
+      </c>
       <c r="F594" s="30">
         <v>45443</v>
       </c>
@@ -84379,6 +84532,86 @@
       <c r="H1108" s="5">
         <v>75</v>
       </c>
+    </row>
+    <row r="1109" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1109" s="34">
+        <v>46199</v>
+      </c>
+      <c r="G1109" s="5">
+        <v>-7</v>
+      </c>
+      <c r="H1109" s="5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1110" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1110" s="34">
+        <v>46200</v>
+      </c>
+      <c r="G1110" s="5">
+        <v>-7</v>
+      </c>
+      <c r="H1110" s="5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1111" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1111" s="34">
+        <v>46201</v>
+      </c>
+      <c r="G1111" s="5">
+        <v>-7</v>
+      </c>
+      <c r="H1111" s="5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1112" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1112" s="34">
+        <v>46202</v>
+      </c>
+      <c r="G1112" s="5">
+        <v>-18</v>
+      </c>
+      <c r="H1112" s="5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="1113" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1113" s="34">
+        <v>46203</v>
+      </c>
+      <c r="G1113" s="5">
+        <v>-23</v>
+      </c>
+      <c r="H1113" s="5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1114" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1114" s="34">
+        <v>46204</v>
+      </c>
+      <c r="G1114" s="5">
+        <v>-38</v>
+      </c>
+      <c r="H1114" s="5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1115" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1115" s="34">
+        <v>46205</v>
+      </c>
+      <c r="G1115" s="5">
+        <v>-64</v>
+      </c>
+      <c r="H1115" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1116" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1116" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/钢铁.xlsx
+++ b/钢铁.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenpe\Desktop\实习202606\平安V2\delink版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F79151-4D24-464C-8298-B7B62A22D206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A60873B-82B4-4557-A6B7-F6B340FB62B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="88">
   <si>
     <t>指标名称</t>
   </si>
@@ -894,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D2884"/>
+  <dimension ref="B2:D2890"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -32605,7 +32605,81 @@
       </c>
     </row>
     <row r="2884" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2884" s="4"/>
+      <c r="B2884" s="4">
+        <v>46206</v>
+      </c>
+      <c r="C2884" s="5">
+        <v>3300</v>
+      </c>
+      <c r="D2884" s="5">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="2885" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2885" s="4">
+        <v>46207</v>
+      </c>
+      <c r="C2885" s="5">
+        <v>3300</v>
+      </c>
+      <c r="D2885" s="5">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="2886" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2886" s="4">
+        <v>46208</v>
+      </c>
+      <c r="C2886" s="5">
+        <v>3300</v>
+      </c>
+      <c r="D2886" s="5">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="2887" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2887" s="4">
+        <v>46209</v>
+      </c>
+      <c r="C2887" s="5">
+        <v>3310</v>
+      </c>
+      <c r="D2887" s="5">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="2888" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2888" s="4">
+        <v>46210</v>
+      </c>
+      <c r="C2888" s="5">
+        <v>3310</v>
+      </c>
+      <c r="D2888" s="5">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="2889" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2889" s="4">
+        <v>46211</v>
+      </c>
+      <c r="C2889" s="5">
+        <v>3330</v>
+      </c>
+      <c r="D2889" s="5">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="2890" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2890" s="4">
+        <v>46212</v>
+      </c>
+      <c r="C2890" s="5">
+        <v>3320</v>
+      </c>
+      <c r="D2890" s="5">
+        <v>3180</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -32615,7 +32689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3CC072-F485-452E-B203-E65436B3141E}">
-  <dimension ref="B2:C2897"/>
+  <dimension ref="B2:C2904"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.265625" style="2" customWidth="1"/>
@@ -55787,7 +55861,63 @@
         <v>46205</v>
       </c>
       <c r="C2897" s="21">
-        <v>97.5</v>
+        <v>98.4</v>
+      </c>
+    </row>
+    <row r="2898" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2898" s="20">
+        <v>46206</v>
+      </c>
+      <c r="C2898" s="21">
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="2899" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2899" s="20">
+        <v>46207</v>
+      </c>
+      <c r="C2899" s="21">
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="2900" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2900" s="20">
+        <v>46208</v>
+      </c>
+      <c r="C2900" s="21">
+        <v>97.9</v>
+      </c>
+    </row>
+    <row r="2901" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2901" s="20">
+        <v>46209</v>
+      </c>
+      <c r="C2901" s="21">
+        <v>98.35</v>
+      </c>
+    </row>
+    <row r="2902" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2902" s="20">
+        <v>46210</v>
+      </c>
+      <c r="C2902" s="21">
+        <v>97.95</v>
+      </c>
+    </row>
+    <row r="2903" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2903" s="20">
+        <v>46211</v>
+      </c>
+      <c r="C2903" s="21">
+        <v>99.1</v>
+      </c>
+    </row>
+    <row r="2904" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2904" s="20">
+        <v>46212</v>
+      </c>
+      <c r="C2904" s="21">
+        <v>99.1</v>
       </c>
     </row>
   </sheetData>
@@ -56921,8 +57051,8 @@
       <c r="M31" s="16">
         <v>1339.58</v>
       </c>
-      <c r="N31" s="36" t="s">
-        <v>87</v>
+      <c r="N31" s="36">
+        <v>1633.92</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.4">
@@ -60665,8 +60795,12 @@
       </c>
     </row>
     <row r="418" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B418" s="12"/>
-      <c r="C418" s="13"/>
+      <c r="B418" s="12">
+        <v>46203</v>
+      </c>
+      <c r="C418" s="13">
+        <v>1628.2</v>
+      </c>
     </row>
     <row r="419" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B419" s="12"/>
@@ -61921,8 +62055,8 @@
       <c r="O31" s="28">
         <v>872.72</v>
       </c>
-      <c r="P31" s="37" t="s">
-        <v>87</v>
+      <c r="P31" s="37">
+        <v>847.03</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.4">
@@ -61962,6 +62096,9 @@
       <c r="O32" s="28">
         <v>868.18999999999994</v>
       </c>
+      <c r="P32" s="37" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B33" s="4">
@@ -68768,7 +68905,15 @@
       </c>
     </row>
     <row r="595" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B595" s="4"/>
+      <c r="B595" s="4">
+        <v>46213</v>
+      </c>
+      <c r="C595" s="5">
+        <v>83.84</v>
+      </c>
+      <c r="D595" s="5">
+        <v>241.27</v>
+      </c>
     </row>
     <row r="596" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B596" s="4"/>
@@ -68787,7 +68932,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A30EC3-E6ED-4809-B571-A03C32366791}">
-  <dimension ref="B2:H1116"/>
+  <dimension ref="B2:H1122"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -78880,6 +79025,12 @@
       </c>
     </row>
     <row r="595" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B595" s="4">
+        <v>46213</v>
+      </c>
+      <c r="C595" s="5">
+        <v>40.26</v>
+      </c>
       <c r="F595" s="30">
         <v>45446</v>
       </c>
@@ -84611,7 +84762,81 @@
       </c>
     </row>
     <row r="1116" spans="6:8" x14ac:dyDescent="0.4">
-      <c r="F1116" s="34"/>
+      <c r="F1116" s="34">
+        <v>46206</v>
+      </c>
+      <c r="G1116" s="5">
+        <v>-61</v>
+      </c>
+      <c r="H1116" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1117" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1117" s="34">
+        <v>46207</v>
+      </c>
+      <c r="G1117" s="5">
+        <v>-61</v>
+      </c>
+      <c r="H1117" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1118" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1118" s="34">
+        <v>46208</v>
+      </c>
+      <c r="G1118" s="5">
+        <v>-61</v>
+      </c>
+      <c r="H1118" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1119" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1119" s="34">
+        <v>46209</v>
+      </c>
+      <c r="G1119" s="5">
+        <v>-72</v>
+      </c>
+      <c r="H1119" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1120" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1120" s="34">
+        <v>46210</v>
+      </c>
+      <c r="G1120" s="5">
+        <v>-69</v>
+      </c>
+      <c r="H1120" s="5">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="1121" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1121" s="34">
+        <v>46211</v>
+      </c>
+      <c r="G1121" s="5">
+        <v>-66</v>
+      </c>
+      <c r="H1121" s="5">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="1122" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1122" s="34">
+        <v>46212</v>
+      </c>
+      <c r="G1122" s="5">
+        <v>-69</v>
+      </c>
+      <c r="H1122" s="5">
+        <v>-19</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/钢铁.xlsx
+++ b/钢铁.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenpe\Desktop\实习202606\平安V2\delink版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A60873B-82B4-4557-A6B7-F6B340FB62B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B08BCA31-9808-4AE6-9D0D-7D0AC8E4A318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -894,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D2890"/>
+  <dimension ref="B2:D2898"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -32681,6 +32681,94 @@
         <v>3180</v>
       </c>
     </row>
+    <row r="2891" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2891" s="4">
+        <v>46213</v>
+      </c>
+      <c r="C2891" s="5">
+        <v>3310</v>
+      </c>
+      <c r="D2891" s="5">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="2892" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2892" s="4">
+        <v>46214</v>
+      </c>
+      <c r="C2892" s="5">
+        <v>3310</v>
+      </c>
+      <c r="D2892" s="5">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="2893" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2893" s="4">
+        <v>46215</v>
+      </c>
+      <c r="C2893" s="5">
+        <v>3310</v>
+      </c>
+      <c r="D2893" s="5">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="2894" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2894" s="4">
+        <v>46216</v>
+      </c>
+      <c r="C2894" s="5">
+        <v>3290</v>
+      </c>
+      <c r="D2894" s="5">
+        <v>3160</v>
+      </c>
+    </row>
+    <row r="2895" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2895" s="4">
+        <v>46217</v>
+      </c>
+      <c r="C2895" s="5">
+        <v>3310</v>
+      </c>
+      <c r="D2895" s="5">
+        <v>3160</v>
+      </c>
+    </row>
+    <row r="2896" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2896" s="4">
+        <v>46218</v>
+      </c>
+      <c r="C2896" s="5">
+        <v>3330</v>
+      </c>
+      <c r="D2896" s="5">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="2897" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2897" s="4">
+        <v>46219</v>
+      </c>
+      <c r="C2897" s="5">
+        <v>3330</v>
+      </c>
+      <c r="D2897" s="5">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="2898" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B2898" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C2898" s="5">
+        <v>3340</v>
+      </c>
+      <c r="D2898" s="5">
+        <v>3180</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32689,7 +32777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB3CC072-F485-452E-B203-E65436B3141E}">
-  <dimension ref="B2:C2904"/>
+  <dimension ref="B2:C2919"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.265625" style="2" customWidth="1"/>
@@ -55917,8 +56005,95 @@
         <v>46212</v>
       </c>
       <c r="C2904" s="21">
-        <v>99.1</v>
-      </c>
+        <v>98.45</v>
+      </c>
+    </row>
+    <row r="2905" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2905" s="20">
+        <v>46213</v>
+      </c>
+      <c r="C2905" s="21">
+        <v>99.05</v>
+      </c>
+    </row>
+    <row r="2906" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2906" s="20">
+        <v>46214</v>
+      </c>
+      <c r="C2906" s="21">
+        <v>99.05</v>
+      </c>
+    </row>
+    <row r="2907" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2907" s="20">
+        <v>46215</v>
+      </c>
+      <c r="C2907" s="21">
+        <v>99.05</v>
+      </c>
+    </row>
+    <row r="2908" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2908" s="20">
+        <v>46216</v>
+      </c>
+      <c r="C2908" s="21">
+        <v>98.1</v>
+      </c>
+    </row>
+    <row r="2909" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2909" s="20">
+        <v>46217</v>
+      </c>
+      <c r="C2909" s="21">
+        <v>99.95</v>
+      </c>
+    </row>
+    <row r="2910" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2910" s="20">
+        <v>46218</v>
+      </c>
+      <c r="C2910" s="21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2911" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2911" s="20">
+        <v>46219</v>
+      </c>
+      <c r="C2911" s="21">
+        <v>99.6</v>
+      </c>
+    </row>
+    <row r="2912" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2912" s="20"/>
+      <c r="C2912" s="21"/>
+    </row>
+    <row r="2913" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2913" s="20"/>
+      <c r="C2913" s="21"/>
+    </row>
+    <row r="2914" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2914" s="20"/>
+      <c r="C2914" s="21"/>
+    </row>
+    <row r="2915" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2915" s="20"/>
+      <c r="C2915" s="21"/>
+    </row>
+    <row r="2916" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2916" s="20"/>
+      <c r="C2916" s="21"/>
+    </row>
+    <row r="2917" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2917" s="20"/>
+      <c r="C2917" s="21"/>
+    </row>
+    <row r="2918" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2918" s="20"/>
+      <c r="C2918" s="21"/>
+    </row>
+    <row r="2919" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B2919" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -57089,11 +57264,11 @@
       <c r="M32" s="16">
         <v>1337.66</v>
       </c>
-      <c r="N32" s="36" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="N32" s="36">
+        <v>1616.0600000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B33" s="8">
         <v>42297</v>
       </c>
@@ -57127,8 +57302,11 @@
       <c r="M33" s="16">
         <v>1336.5</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="N33" s="36" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B34" s="8">
         <v>42308</v>
       </c>
@@ -57163,7 +57341,7 @@
         <v>1351.89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B35" s="8">
         <v>42318</v>
       </c>
@@ -57198,7 +57376,7 @@
         <v>1375.36</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B36" s="8">
         <v>42328</v>
       </c>
@@ -57233,7 +57411,7 @@
         <v>1415.97</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B37" s="8">
         <v>42338</v>
       </c>
@@ -57268,7 +57446,7 @@
         <v>1441.04</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B38" s="8">
         <v>42348</v>
       </c>
@@ -57303,7 +57481,7 @@
         <v>1467.88</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B39" s="8">
         <v>42358</v>
       </c>
@@ -57338,7 +57516,7 @@
         <v>1500.7</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B40" s="8">
         <v>42369</v>
       </c>
@@ -57373,7 +57551,7 @@
         <v>1514.61</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B41" s="8">
         <v>42379</v>
       </c>
@@ -57408,7 +57586,7 @@
         <v>1519.74</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B42" s="8">
         <v>42389</v>
       </c>
@@ -57443,7 +57621,7 @@
         <v>1510.61</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B43" s="8">
         <v>42400</v>
       </c>
@@ -57478,7 +57656,7 @@
         <v>1472.86</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B44" s="8">
         <v>42410</v>
       </c>
@@ -57513,7 +57691,7 @@
         <v>1600.72</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B45" s="8">
         <v>42420</v>
       </c>
@@ -57548,7 +57726,7 @@
         <v>1582.26</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B46" s="8">
         <v>42429</v>
       </c>
@@ -57583,7 +57761,7 @@
         <v>1554.87</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B47" s="8">
         <v>42439</v>
       </c>
@@ -57618,7 +57796,7 @@
         <v>1513.76</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B48" s="8">
         <v>42449</v>
       </c>
@@ -60803,8 +60981,12 @@
       </c>
     </row>
     <row r="419" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B419" s="12"/>
-      <c r="C419" s="13"/>
+      <c r="B419" s="12">
+        <v>46213</v>
+      </c>
+      <c r="C419" s="13">
+        <v>1677</v>
+      </c>
     </row>
     <row r="420" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B420" s="12"/>
@@ -62096,11 +62278,11 @@
       <c r="O32" s="28">
         <v>868.18999999999994</v>
       </c>
-      <c r="P32" s="37" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="P32" s="37">
+        <v>825.81999999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B33" s="4">
         <v>42209</v>
       </c>
@@ -62137,8 +62319,11 @@
       <c r="O33" s="28">
         <v>866.97</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="P33" s="37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B34" s="4">
         <v>42216</v>
       </c>
@@ -62176,7 +62361,7 @@
         <v>867.42000000000007</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B35" s="4">
         <v>42223</v>
       </c>
@@ -62214,7 +62399,7 @@
         <v>869.21</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B36" s="4">
         <v>42230</v>
       </c>
@@ -62252,7 +62437,7 @@
         <v>871.62999999999988</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B37" s="4">
         <v>42237</v>
       </c>
@@ -62290,7 +62475,7 @@
         <v>878.06000000000006</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B38" s="4">
         <v>42244</v>
       </c>
@@ -62328,7 +62513,7 @@
         <v>884.61</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B39" s="4">
         <v>42251</v>
       </c>
@@ -62366,7 +62551,7 @@
         <v>860.65</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B40" s="4">
         <v>42258</v>
       </c>
@@ -62404,7 +62589,7 @@
         <v>857.24</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B41" s="4">
         <v>42265</v>
       </c>
@@ -62442,7 +62627,7 @@
         <v>855.46</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B42" s="4">
         <v>42272</v>
       </c>
@@ -62480,7 +62665,7 @@
         <v>864.93000000000018</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B43" s="4">
         <v>42286</v>
       </c>
@@ -62518,7 +62703,7 @@
         <v>867.06999999999994</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B44" s="4">
         <v>42293</v>
       </c>
@@ -62556,7 +62741,7 @@
         <v>863.31</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B45" s="4">
         <v>42300</v>
       </c>
@@ -62594,7 +62779,7 @@
         <v>856.94999999999993</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B46" s="4">
         <v>42307</v>
       </c>
@@ -62632,7 +62817,7 @@
         <v>865.31999999999982</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B47" s="4">
         <v>42314</v>
       </c>
@@ -62670,7 +62855,7 @@
         <v>875.29000000000008</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B48" s="4">
         <v>42321</v>
       </c>
@@ -68916,7 +69101,15 @@
       </c>
     </row>
     <row r="596" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B596" s="4"/>
+      <c r="B596" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C596" s="5">
+        <v>82.73</v>
+      </c>
+      <c r="D596" s="5">
+        <v>239.21</v>
+      </c>
     </row>
     <row r="597" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B597" s="4"/>
@@ -68932,7 +69125,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A30EC3-E6ED-4809-B571-A03C32366791}">
-  <dimension ref="B2:H1122"/>
+  <dimension ref="B2:H1129"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
@@ -79042,6 +79235,12 @@
       </c>
     </row>
     <row r="596" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B596" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C596" s="5">
+        <v>37.229999999999997</v>
+      </c>
       <c r="F596" s="30">
         <v>45447</v>
       </c>
@@ -79053,6 +79252,7 @@
       </c>
     </row>
     <row r="597" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B597" s="4"/>
       <c r="F597" s="30">
         <v>45448</v>
       </c>
@@ -79064,6 +79264,7 @@
       </c>
     </row>
     <row r="598" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B598" s="4"/>
       <c r="F598" s="30">
         <v>45449</v>
       </c>
@@ -79075,6 +79276,7 @@
       </c>
     </row>
     <row r="599" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B599" s="4"/>
       <c r="F599" s="30">
         <v>45450</v>
       </c>
@@ -79086,6 +79288,7 @@
       </c>
     </row>
     <row r="600" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B600" s="4"/>
       <c r="F600" s="30">
         <v>45454</v>
       </c>
@@ -79097,6 +79300,7 @@
       </c>
     </row>
     <row r="601" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B601" s="4"/>
       <c r="F601" s="30">
         <v>45455</v>
       </c>
@@ -79108,6 +79312,7 @@
       </c>
     </row>
     <row r="602" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B602" s="4"/>
       <c r="F602" s="30">
         <v>45456</v>
       </c>
@@ -79119,6 +79324,7 @@
       </c>
     </row>
     <row r="603" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B603" s="4"/>
       <c r="F603" s="30">
         <v>45457</v>
       </c>
@@ -79130,6 +79336,7 @@
       </c>
     </row>
     <row r="604" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B604" s="4"/>
       <c r="F604" s="30">
         <v>45460</v>
       </c>
@@ -79141,6 +79348,7 @@
       </c>
     </row>
     <row r="605" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B605" s="4"/>
       <c r="F605" s="30">
         <v>45461</v>
       </c>
@@ -79152,6 +79360,7 @@
       </c>
     </row>
     <row r="606" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B606" s="4"/>
       <c r="F606" s="30">
         <v>45462</v>
       </c>
@@ -79163,6 +79372,7 @@
       </c>
     </row>
     <row r="607" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B607" s="4"/>
       <c r="F607" s="30">
         <v>45463</v>
       </c>
@@ -79174,6 +79384,7 @@
       </c>
     </row>
     <row r="608" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B608" s="4"/>
       <c r="F608" s="30">
         <v>45464</v>
       </c>
@@ -79184,7 +79395,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="609" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="609" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B609" s="4"/>
       <c r="F609" s="30">
         <v>45467</v>
       </c>
@@ -79195,7 +79407,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="610" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="610" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B610" s="4"/>
       <c r="F610" s="30">
         <v>45468</v>
       </c>
@@ -79206,7 +79419,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="611" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="611" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B611" s="4"/>
       <c r="F611" s="30">
         <v>45469</v>
       </c>
@@ -79217,7 +79431,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="612" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="612" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B612" s="4"/>
       <c r="F612" s="30">
         <v>45470</v>
       </c>
@@ -79228,7 +79443,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="613" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="613" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B613" s="4"/>
       <c r="F613" s="30">
         <v>45471</v>
       </c>
@@ -79239,7 +79455,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="614" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="614" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B614" s="4"/>
       <c r="F614" s="30">
         <v>45474</v>
       </c>
@@ -79250,7 +79467,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="615" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="615" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F615" s="30">
         <v>45475</v>
       </c>
@@ -79261,7 +79478,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="616" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="616" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F616" s="30">
         <v>45476</v>
       </c>
@@ -79272,7 +79489,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="617" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="617" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F617" s="30">
         <v>45477</v>
       </c>
@@ -79283,7 +79500,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="618" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="618" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F618" s="30">
         <v>45478</v>
       </c>
@@ -79294,7 +79511,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="619" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="619" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F619" s="30">
         <v>45481</v>
       </c>
@@ -79305,7 +79522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="620" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="620" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F620" s="30">
         <v>45482</v>
       </c>
@@ -79316,7 +79533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="621" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="621" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F621" s="30">
         <v>45483</v>
       </c>
@@ -79327,7 +79544,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="622" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="622" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F622" s="30">
         <v>45484</v>
       </c>
@@ -79338,7 +79555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="623" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="623" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F623" s="30">
         <v>45485</v>
       </c>
@@ -79349,7 +79566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="6:8" x14ac:dyDescent="0.4">
+    <row r="624" spans="2:8" x14ac:dyDescent="0.4">
       <c r="F624" s="30">
         <v>45488</v>
       </c>
@@ -84836,6 +85053,83 @@
       </c>
       <c r="H1122" s="5">
         <v>-19</v>
+      </c>
+    </row>
+    <row r="1123" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1123" s="34">
+        <v>46213</v>
+      </c>
+      <c r="G1123" s="5">
+        <v>-74</v>
+      </c>
+      <c r="H1123" s="5">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="1124" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1124" s="34">
+        <v>46214</v>
+      </c>
+      <c r="G1124" s="5">
+        <v>-74</v>
+      </c>
+      <c r="H1124" s="5">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="1125" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1125" s="34">
+        <v>46215</v>
+      </c>
+      <c r="G1125" s="5">
+        <v>-74</v>
+      </c>
+      <c r="H1125" s="5">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="1126" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1126" s="34">
+        <v>46216</v>
+      </c>
+      <c r="G1126" s="5">
+        <v>-92</v>
+      </c>
+      <c r="H1126" s="5">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="1127" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1127" s="34">
+        <v>46217</v>
+      </c>
+      <c r="G1127" s="5">
+        <v>-96</v>
+      </c>
+      <c r="H1127" s="5">
+        <v>-31</v>
+      </c>
+    </row>
+    <row r="1128" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1128" s="34">
+        <v>46218</v>
+      </c>
+      <c r="G1128" s="5">
+        <v>-88</v>
+      </c>
+      <c r="H1128" s="5">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="1129" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F1129" s="34">
+        <v>46219</v>
+      </c>
+      <c r="G1129" s="5">
+        <v>-83</v>
+      </c>
+      <c r="H1129" s="5">
+        <v>-18</v>
       </c>
     </row>
   </sheetData>
